--- a/reglas de negocio/Registro_Reglas_Negocio_Overfore_v1.2.xlsx
+++ b/reglas de negocio/Registro_Reglas_Negocio_Overfore_v1.2.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bases Técnicas del Caso 01, v1.0 · Consolidado de decisiones del numeral 16.1 · Subdocumento 3 v1.4 · Catálogo de requerimientos v2.4 · Registro de supuestos v1.3</t>
+          <t>Bases Técnicas del Caso 01, v1.0 · Consolidado de decisiones del numeral 16.1 · Subdocumento 3 v1.4 · Catálogo de requerimientos v2.4 · Registro de supuestos v1.4</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1.2 — 30 de agosto de 2026. Alinea las referencias cruzadas a la v1.4 del Subdocumento 3 y a la v2.4 del catálogo, y suma RF-MIG-008 a la regla RN-28 tras el desdoblamiento de la migración entre etapas</t>
+          <t>1.2 — 30 de agosto de 2026. Alinea las referencias cruzadas a la v1.4 del Subdocumento 3 y a la v2.4 del catálogo, y suma RF-MIG-008 a la regla RN-28 tras el desdoblamiento de la migración entre etapas. Revisión de consistencia del 1 de septiembre de 2026: RN-02 y RN-04 se alinean con las exclusiones del apartado 3 del Subdocumento 3 v1.4; RN-03, RN-06, RN-10, RN-14 y RN-16 dejan de citar como decisiones del numeral 16.1 los vacíos adicionales del propio proponente; RN-27 corrige el documento de origen</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>El operador puede levantar el aviso de cambio de material con el botón único de cabina; el prorrateo se evalúa en la Etapa 2 si la marcha blanca demuestra que la proporción es material.</t>
+          <t>El operador puede levantar el aviso de cambio de material con el botón único de cabina. El prorrateo automático está excluido del Contrato en ambas etapas: la marca de borde permite al CLIENTE conocer en marcha blanca qué proporción de viajes es de borde y decidir con esa evidencia si lo solicita como cambio conforme al Artículo 72.º de las Bases Administrativas.</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Decisión 16.1 n.º 16 · Cap. 3 (acopio de 25.000 t) · SUP-16</t>
+          <t>Vacío adicional n.º 16 del Consolidado 16.1 (identificado por el PROPONENTE, no listado en el numeral 16.1) · Cap. 3 (acopio de 25.000 t) · SUP-16</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Sí, el factor de corrección</t>
+          <t>No. El factor de corrección de pesaje está excluido del Contrato (cambio Art. 72.º)</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Decisión 16.1 n.º 15 · Cap. C, glosario · SUP-15</t>
+          <t>Vacío adicional n.º 15 del Consolidado 16.1 (identificado por el PROPONENTE, no listado en el numeral 16.1) · Cap. C, glosario · SUP-15</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Decisión 16.1 n.º 15 · Cap. 8, Sanhueza · SUP-15</t>
+          <t>Vacío adicional n.º 15 del Consolidado 16.1 (identificado por el PROPONENTE, no listado en el numeral 16.1) · Cap. 8, Sanhueza · SUP-15</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Decisión 16.1 n.º 18 · Cap. 12, comercialización de concentrados · Cap. 2.1</t>
+          <t>Vacío adicional n.º 18 del Consolidado 16.1 (identificado por el PROPONENTE, no listado en el numeral 16.1) · Cap. 12, comercialización de concentrados · Cap. 2.1</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Decisión 16.1 n.º 17 · Cap. 9.1 · SUP-17</t>
+          <t>Vacío adicional n.º 17 del Consolidado 16.1 (identificado por el PROPONENTE, no listado en el numeral 16.1) · Cap. 9.1 · SUP-17</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Cap. 15, RT-16.02 y RT-16.03 · Cap. 17.1</t>
+          <t>Bases Técnicas Transversales, RT-16.02 y RT-16.03 · Cap. 17.1</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">

--- a/reglas de negocio/Registro_Reglas_Negocio_Overfore_v1.2.xlsx
+++ b/reglas de negocio/Registro_Reglas_Negocio_Overfore_v1.2.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bases Técnicas del Caso 01, v1.0 · Consolidado de decisiones del numeral 16.1 · Subdocumento 3 v1.4 · Catálogo de requerimientos v2.4 · Registro de supuestos v1.4</t>
+          <t>Bases Técnicas del Caso 01, v1.0 · Consolidado de decisiones del numeral 16.1 · Subdocumento 3 v1.4 · Catálogo de requerimientos v2.4 · Registro de supuestos v1.6</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1.2 — 30 de agosto de 2026. Alinea las referencias cruzadas a la v1.4 del Subdocumento 3 y a la v2.4 del catálogo, y suma RF-MIG-008 a la regla RN-28 tras el desdoblamiento de la migración entre etapas. Revisión de consistencia del 1 de septiembre de 2026: RN-02 y RN-04 se alinean con las exclusiones del apartado 3 del Subdocumento 3 v1.4; RN-03, RN-06, RN-10, RN-14 y RN-16 dejan de citar como decisiones del numeral 16.1 los vacíos adicionales del propio proponente; RN-27 corrige el documento de origen</t>
+          <t>1.2 — 30 de agosto de 2026. Alinea las referencias cruzadas a la v1.4 del Subdocumento 3 y a la v2.4 del catálogo, y suma RF-MIG-008 a la regla RN-28 tras el desdoblamiento de la migración entre etapas. Revisión de consistencia del 1 de septiembre de 2026: RN-02 y RN-04 se alinean con las exclusiones del apartado 3 del Subdocumento 3 v1.4; RN-03, RN-06, RN-10, RN-14 y RN-16 dejan de citar como decisiones del numeral 16.1 los vacíos adicionales del propio proponente; RN-27 corrige el documento de origen. Revisión de consistencia del 4 de septiembre de 2026: RN-28 incorpora la retención del asiento de auditoría y de los datos maestros de la plataforma, que el Capítulo 15 no fija y que el Subdocumento 5 comprometía en diez años sin regla que la sostuviera; y se actualiza la versión citada del Registro de supuestos, hoy v1.6</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Seguridad y salud ocupacional 10 años; ambientales y de monitoreo 10; trazabilidad de mineral y embarques 10; operacionales 5; tributarios 7.</t>
+          <t>Seguridad y salud ocupacional 10 años; ambientales y de monitoreo 10; trazabilidad de mineral y embarques 10; operacionales 5; tributarios 7. Auditoría y datos maestros de la plataforma —asiento de auditoría, parámetro y regla versionados y dispositivo inventariado— 10 años: el Capítulo 15 no les fija plazo y el PROPONENTE los alinea con la retención mayor que ese mismo capítulo exige a la trazabilidad y a los registros de seguridad.</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
